--- a/data/sheet_template/BTU_AI_Passport_Test_Sheet.xlsx
+++ b/data/sheet_template/BTU_AI_Passport_Test_Sheet.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -828,6 +828,834 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BTU-T-0001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Giorgi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kapanadze</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>გიორგი</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>კაპანაძე</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>giorgi.kapanadze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Business Administration (Management)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BTU-T-0002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mariam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Beridze</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>მარიამ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ბერიძე</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>mariam.beridze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Business Administration (Finance)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BTU-T-0003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nino</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Maisuradze</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ნინო</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>მაისურაძე</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nino.maisuradze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Information Technologies</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BTU-T-0004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Saba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Japaridze</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>საბა</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ჯაფარიძე</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>saba.japaridze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Digital Marketing</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BTU-T-0005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kiknadze</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ანა</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>კიკნაძე</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ana.kiknadze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Computer Science and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BTU-T-0006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Davit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Metreveli</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>დავით</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>მეტრეველი</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>davit.metreveli@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Psychology in the Digital World</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BTU-T-0007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Salome</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chkheidze</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>სალომე</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ჩხეიძე</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>salome.chkheidze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Business Administration and Modern Technologies</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BTU-T-0008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Luka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kipiani</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ლუკა</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ყიფიანი</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>luka.kipiani@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Information Systems Management - DevOps</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BTU-T-0009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tamar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gogoladze</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>თამარ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>გოგოლაძე</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>tamar.gogoladze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Data-Driven Digital Marketing</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BTU-T-0010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Irakli</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Samkharadze</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ირაკლი</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>სამხარაძე</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>irakli.samkharadze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>International Security and Technologies</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BTU-T-0011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Elene</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lomidze</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ელენე</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ლომიძე</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>elene.lomidze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Business Administration (Management)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BTU-T-0012</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nikoloz</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gelashvili</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ნიკოლოზ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>გელაშვილი</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nikoloz.gelashvili@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Business Administration (Finance)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BTU-T-0013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ketevan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Abashidze</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ქეთევან</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>აბაშიძე</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ketevan.abashidze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Information Technologies</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BTU-T-0014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aleksandre</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mchedlishvili</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ალექსანდრე</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>მჭედლიშვილი</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>aleksandre.mchedlishvili@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Digital Marketing</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BTU-T-0021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Luka</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Japaridze</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ლუკა</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ჯაფარიძე</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>luka.japaridze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Business Administration and Modern Technologies</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BTU-T-0022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Salome</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Abashidze</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>სალომე</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>აბაშიძე</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>salome.abashidze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Information Systems Management - DevOps</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BTU-T-0023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kiknadze</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>დათო</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>კიკნაძე</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>dato.kiknadze@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Data-Driven Digital Marketing</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BTU-T-0024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elene</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tsiklauri</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ელენე</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ციკლაური</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>elene.tsiklauri@btu.edu.ge</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>International Security and Technologies</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
